--- a/artfynd/A 35667-2026 artfynd.xlsx
+++ b/artfynd/A 35667-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136741579</v>
       </c>
       <c r="B2" t="n">
-        <v>92299</v>
+        <v>92304</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>136741574</v>
       </c>
       <c r="B3" t="n">
-        <v>91113</v>
+        <v>91115</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136741584</v>
       </c>
       <c r="B4" t="n">
-        <v>91113</v>
+        <v>91115</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136741571</v>
       </c>
       <c r="B5" t="n">
-        <v>92159</v>
+        <v>92164</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136741596</v>
       </c>
       <c r="B6" t="n">
-        <v>93398</v>
+        <v>93403</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136741597</v>
       </c>
       <c r="B7" t="n">
-        <v>93416</v>
+        <v>93421</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>136741600</v>
       </c>
       <c r="B8" t="n">
-        <v>93416</v>
+        <v>93421</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>136741585</v>
       </c>
       <c r="B9" t="n">
-        <v>90891</v>
+        <v>90893</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>136741587</v>
       </c>
       <c r="B10" t="n">
-        <v>90891</v>
+        <v>90893</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>136741570</v>
       </c>
       <c r="B11" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>136741575</v>
       </c>
       <c r="B12" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136741576</v>
       </c>
       <c r="B13" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>136741582</v>
       </c>
       <c r="B14" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>136741583</v>
       </c>
       <c r="B15" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>136741595</v>
       </c>
       <c r="B16" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>136741591</v>
       </c>
       <c r="B17" t="n">
-        <v>80593</v>
+        <v>80595</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>136741592</v>
       </c>
       <c r="B18" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>136741577</v>
       </c>
       <c r="B19" t="n">
-        <v>58110</v>
+        <v>58112</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>136741578</v>
       </c>
       <c r="B20" t="n">
-        <v>98218</v>
+        <v>98223</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>136741588</v>
       </c>
       <c r="B21" t="n">
-        <v>98218</v>
+        <v>98223</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>136741589</v>
       </c>
       <c r="B22" t="n">
-        <v>98218</v>
+        <v>98223</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>136741590</v>
       </c>
       <c r="B23" t="n">
-        <v>98218</v>
+        <v>98223</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>136741569</v>
       </c>
       <c r="B24" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 35667-2026 artfynd.xlsx
+++ b/artfynd/A 35667-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136741579</v>
       </c>
       <c r="B2" t="n">
-        <v>92304</v>
+        <v>92306</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>136741574</v>
       </c>
       <c r="B3" t="n">
-        <v>91115</v>
+        <v>91117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136741584</v>
       </c>
       <c r="B4" t="n">
-        <v>91115</v>
+        <v>91117</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136741571</v>
       </c>
       <c r="B5" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136741596</v>
       </c>
       <c r="B6" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136741597</v>
       </c>
       <c r="B7" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>136741600</v>
       </c>
       <c r="B8" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>136741585</v>
       </c>
       <c r="B9" t="n">
-        <v>90893</v>
+        <v>90895</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>136741587</v>
       </c>
       <c r="B10" t="n">
-        <v>90893</v>
+        <v>90895</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>136741578</v>
       </c>
       <c r="B20" t="n">
-        <v>98223</v>
+        <v>98225</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>136741588</v>
       </c>
       <c r="B21" t="n">
-        <v>98223</v>
+        <v>98225</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>136741589</v>
       </c>
       <c r="B22" t="n">
-        <v>98223</v>
+        <v>98225</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>136741590</v>
       </c>
       <c r="B23" t="n">
-        <v>98223</v>
+        <v>98225</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>136741569</v>
       </c>
       <c r="B24" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 35667-2026 artfynd.xlsx
+++ b/artfynd/A 35667-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136741579</v>
       </c>
       <c r="B2" t="n">
-        <v>92306</v>
+        <v>92308</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>136741574</v>
       </c>
       <c r="B3" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136741584</v>
       </c>
       <c r="B4" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136741571</v>
       </c>
       <c r="B5" t="n">
-        <v>92166</v>
+        <v>92168</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136741596</v>
       </c>
       <c r="B6" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136741597</v>
       </c>
       <c r="B7" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>136741600</v>
       </c>
       <c r="B8" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>136741585</v>
       </c>
       <c r="B9" t="n">
-        <v>90895</v>
+        <v>90897</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>136741587</v>
       </c>
       <c r="B10" t="n">
-        <v>90895</v>
+        <v>90897</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>136741570</v>
       </c>
       <c r="B11" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>136741575</v>
       </c>
       <c r="B12" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136741576</v>
       </c>
       <c r="B13" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>136741582</v>
       </c>
       <c r="B14" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>136741583</v>
       </c>
       <c r="B15" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>136741595</v>
       </c>
       <c r="B16" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>136741591</v>
       </c>
       <c r="B17" t="n">
-        <v>80595</v>
+        <v>80599</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>136741578</v>
       </c>
       <c r="B20" t="n">
-        <v>98225</v>
+        <v>98231</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>136741588</v>
       </c>
       <c r="B21" t="n">
-        <v>98225</v>
+        <v>98231</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>136741589</v>
       </c>
       <c r="B22" t="n">
-        <v>98225</v>
+        <v>98231</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>136741590</v>
       </c>
       <c r="B23" t="n">
-        <v>98225</v>
+        <v>98231</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>136741569</v>
       </c>
       <c r="B24" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 35667-2026 artfynd.xlsx
+++ b/artfynd/A 35667-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136741579</v>
       </c>
       <c r="B2" t="n">
-        <v>92308</v>
+        <v>92310</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>136741574</v>
       </c>
       <c r="B3" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136741584</v>
       </c>
       <c r="B4" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136741571</v>
       </c>
       <c r="B5" t="n">
-        <v>92168</v>
+        <v>92170</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136741596</v>
       </c>
       <c r="B6" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136741597</v>
       </c>
       <c r="B7" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>136741600</v>
       </c>
       <c r="B8" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>136741585</v>
       </c>
       <c r="B9" t="n">
-        <v>90897</v>
+        <v>90899</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>136741587</v>
       </c>
       <c r="B10" t="n">
-        <v>90897</v>
+        <v>90899</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>136741570</v>
       </c>
       <c r="B11" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>136741575</v>
       </c>
       <c r="B12" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136741576</v>
       </c>
       <c r="B13" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>136741582</v>
       </c>
       <c r="B14" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>136741583</v>
       </c>
       <c r="B15" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>136741595</v>
       </c>
       <c r="B16" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>136741591</v>
       </c>
       <c r="B17" t="n">
-        <v>80599</v>
+        <v>80601</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>136741578</v>
       </c>
       <c r="B20" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>136741588</v>
       </c>
       <c r="B21" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>136741589</v>
       </c>
       <c r="B22" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>136741590</v>
       </c>
       <c r="B23" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>136741569</v>
       </c>
       <c r="B24" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 35667-2026 artfynd.xlsx
+++ b/artfynd/A 35667-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136741579</v>
       </c>
       <c r="B2" t="n">
-        <v>92310</v>
+        <v>92311</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>136741574</v>
       </c>
       <c r="B3" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136741584</v>
       </c>
       <c r="B4" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136741571</v>
       </c>
       <c r="B5" t="n">
-        <v>92170</v>
+        <v>92171</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136741596</v>
       </c>
       <c r="B6" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136741597</v>
       </c>
       <c r="B7" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>136741600</v>
       </c>
       <c r="B8" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>136741585</v>
       </c>
       <c r="B9" t="n">
-        <v>90899</v>
+        <v>90900</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>136741587</v>
       </c>
       <c r="B10" t="n">
-        <v>90899</v>
+        <v>90900</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>136741570</v>
       </c>
       <c r="B11" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>136741575</v>
       </c>
       <c r="B12" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136741576</v>
       </c>
       <c r="B13" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>136741582</v>
       </c>
       <c r="B14" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>136741583</v>
       </c>
       <c r="B15" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>136741595</v>
       </c>
       <c r="B16" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>136741591</v>
       </c>
       <c r="B17" t="n">
-        <v>80601</v>
+        <v>80602</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>136741578</v>
       </c>
       <c r="B20" t="n">
-        <v>98233</v>
+        <v>98234</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>136741588</v>
       </c>
       <c r="B21" t="n">
-        <v>98233</v>
+        <v>98234</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>136741589</v>
       </c>
       <c r="B22" t="n">
-        <v>98233</v>
+        <v>98234</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>136741590</v>
       </c>
       <c r="B23" t="n">
-        <v>98233</v>
+        <v>98234</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>136741569</v>
       </c>
       <c r="B24" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 35667-2026 artfynd.xlsx
+++ b/artfynd/A 35667-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136741579</v>
       </c>
       <c r="B2" t="n">
-        <v>92311</v>
+        <v>92317</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>136741574</v>
       </c>
       <c r="B3" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136741584</v>
       </c>
       <c r="B4" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136741571</v>
       </c>
       <c r="B5" t="n">
-        <v>92171</v>
+        <v>92177</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136741596</v>
       </c>
       <c r="B6" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136741597</v>
       </c>
       <c r="B7" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>136741600</v>
       </c>
       <c r="B8" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>136741585</v>
       </c>
       <c r="B9" t="n">
-        <v>90900</v>
+        <v>90906</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>136741587</v>
       </c>
       <c r="B10" t="n">
-        <v>90900</v>
+        <v>90906</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>136741578</v>
       </c>
       <c r="B20" t="n">
-        <v>98234</v>
+        <v>98240</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>136741588</v>
       </c>
       <c r="B21" t="n">
-        <v>98234</v>
+        <v>98240</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>136741589</v>
       </c>
       <c r="B22" t="n">
-        <v>98234</v>
+        <v>98240</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>136741590</v>
       </c>
       <c r="B23" t="n">
-        <v>98234</v>
+        <v>98240</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>136741569</v>
       </c>
       <c r="B24" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 35667-2026 artfynd.xlsx
+++ b/artfynd/A 35667-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136741579</v>
       </c>
       <c r="B2" t="n">
-        <v>92317</v>
+        <v>92321</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>136741574</v>
       </c>
       <c r="B3" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136741584</v>
       </c>
       <c r="B4" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136741571</v>
       </c>
       <c r="B5" t="n">
-        <v>92177</v>
+        <v>92181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136741596</v>
       </c>
       <c r="B6" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136741597</v>
       </c>
       <c r="B7" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>136741600</v>
       </c>
       <c r="B8" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>136741585</v>
       </c>
       <c r="B9" t="n">
-        <v>90906</v>
+        <v>90910</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>136741587</v>
       </c>
       <c r="B10" t="n">
-        <v>90906</v>
+        <v>90910</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>136741570</v>
       </c>
       <c r="B11" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>136741575</v>
       </c>
       <c r="B12" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136741576</v>
       </c>
       <c r="B13" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>136741582</v>
       </c>
       <c r="B14" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>136741583</v>
       </c>
       <c r="B15" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>136741595</v>
       </c>
       <c r="B16" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>136741591</v>
       </c>
       <c r="B17" t="n">
-        <v>80602</v>
+        <v>80604</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>136741578</v>
       </c>
       <c r="B20" t="n">
-        <v>98240</v>
+        <v>98244</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>136741588</v>
       </c>
       <c r="B21" t="n">
-        <v>98240</v>
+        <v>98244</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>136741589</v>
       </c>
       <c r="B22" t="n">
-        <v>98240</v>
+        <v>98244</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>136741590</v>
       </c>
       <c r="B23" t="n">
-        <v>98240</v>
+        <v>98244</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>136741569</v>
       </c>
       <c r="B24" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 35667-2026 artfynd.xlsx
+++ b/artfynd/A 35667-2026 artfynd.xlsx
@@ -2738,7 +2738,7 @@
         <v>136741578</v>
       </c>
       <c r="B20" t="n">
-        <v>98244</v>
+        <v>98246</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>136741588</v>
       </c>
       <c r="B21" t="n">
-        <v>98244</v>
+        <v>98246</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>136741589</v>
       </c>
       <c r="B22" t="n">
-        <v>98244</v>
+        <v>98246</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>136741590</v>
       </c>
       <c r="B23" t="n">
-        <v>98244</v>
+        <v>98246</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>136741569</v>
       </c>
       <c r="B24" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 35667-2026 artfynd.xlsx
+++ b/artfynd/A 35667-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136741579</v>
       </c>
       <c r="B2" t="n">
-        <v>92321</v>
+        <v>92323</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>136741574</v>
       </c>
       <c r="B3" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136741584</v>
       </c>
       <c r="B4" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136741571</v>
       </c>
       <c r="B5" t="n">
-        <v>92181</v>
+        <v>92183</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136741596</v>
       </c>
       <c r="B6" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136741597</v>
       </c>
       <c r="B7" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>136741600</v>
       </c>
       <c r="B8" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>136741585</v>
       </c>
       <c r="B9" t="n">
-        <v>90910</v>
+        <v>90912</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>136741587</v>
       </c>
       <c r="B10" t="n">
-        <v>90910</v>
+        <v>90912</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>136741570</v>
       </c>
       <c r="B11" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>136741575</v>
       </c>
       <c r="B12" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136741576</v>
       </c>
       <c r="B13" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>136741582</v>
       </c>
       <c r="B14" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>136741583</v>
       </c>
       <c r="B15" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>136741595</v>
       </c>
       <c r="B16" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>136741591</v>
       </c>
       <c r="B17" t="n">
-        <v>80604</v>
+        <v>80607</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>136741578</v>
       </c>
       <c r="B20" t="n">
-        <v>98246</v>
+        <v>98248</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>136741588</v>
       </c>
       <c r="B21" t="n">
-        <v>98246</v>
+        <v>98248</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>136741589</v>
       </c>
       <c r="B22" t="n">
-        <v>98246</v>
+        <v>98248</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>136741590</v>
       </c>
       <c r="B23" t="n">
-        <v>98246</v>
+        <v>98248</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>136741569</v>
       </c>
       <c r="B24" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 35667-2026 artfynd.xlsx
+++ b/artfynd/A 35667-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136741579</v>
       </c>
       <c r="B2" t="n">
-        <v>92323</v>
+        <v>92336</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>136741574</v>
       </c>
       <c r="B3" t="n">
-        <v>91134</v>
+        <v>91147</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136741584</v>
       </c>
       <c r="B4" t="n">
-        <v>91134</v>
+        <v>91147</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136741571</v>
       </c>
       <c r="B5" t="n">
-        <v>92183</v>
+        <v>92196</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136741596</v>
       </c>
       <c r="B6" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136741597</v>
       </c>
       <c r="B7" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>136741600</v>
       </c>
       <c r="B8" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>136741585</v>
       </c>
       <c r="B9" t="n">
-        <v>90912</v>
+        <v>90925</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>136741587</v>
       </c>
       <c r="B10" t="n">
-        <v>90912</v>
+        <v>90925</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>136741570</v>
       </c>
       <c r="B11" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>136741575</v>
       </c>
       <c r="B12" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136741576</v>
       </c>
       <c r="B13" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>136741582</v>
       </c>
       <c r="B14" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>136741583</v>
       </c>
       <c r="B15" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>136741595</v>
       </c>
       <c r="B16" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>136741591</v>
       </c>
       <c r="B17" t="n">
-        <v>80607</v>
+        <v>80620</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>136741592</v>
       </c>
       <c r="B18" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>136741577</v>
       </c>
       <c r="B19" t="n">
-        <v>58112</v>
+        <v>58125</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>136741578</v>
       </c>
       <c r="B20" t="n">
-        <v>98248</v>
+        <v>98261</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>136741588</v>
       </c>
       <c r="B21" t="n">
-        <v>98248</v>
+        <v>98261</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>136741589</v>
       </c>
       <c r="B22" t="n">
-        <v>98248</v>
+        <v>98261</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>136741590</v>
       </c>
       <c r="B23" t="n">
-        <v>98248</v>
+        <v>98261</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>136741569</v>
       </c>
       <c r="B24" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 35667-2026 artfynd.xlsx
+++ b/artfynd/A 35667-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136741579</v>
       </c>
       <c r="B2" t="n">
-        <v>92336</v>
+        <v>92338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>136741574</v>
       </c>
       <c r="B3" t="n">
-        <v>91147</v>
+        <v>91149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136741584</v>
       </c>
       <c r="B4" t="n">
-        <v>91147</v>
+        <v>91149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136741571</v>
       </c>
       <c r="B5" t="n">
-        <v>92196</v>
+        <v>92198</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136741596</v>
       </c>
       <c r="B6" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136741597</v>
       </c>
       <c r="B7" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>136741600</v>
       </c>
       <c r="B8" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>136741585</v>
       </c>
       <c r="B9" t="n">
-        <v>90925</v>
+        <v>90927</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>136741587</v>
       </c>
       <c r="B10" t="n">
-        <v>90925</v>
+        <v>90927</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>136741570</v>
       </c>
       <c r="B11" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>136741575</v>
       </c>
       <c r="B12" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136741576</v>
       </c>
       <c r="B13" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>136741582</v>
       </c>
       <c r="B14" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>136741583</v>
       </c>
       <c r="B15" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>136741595</v>
       </c>
       <c r="B16" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>136741591</v>
       </c>
       <c r="B17" t="n">
-        <v>80620</v>
+        <v>80622</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>136741592</v>
       </c>
       <c r="B18" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>136741577</v>
       </c>
       <c r="B19" t="n">
-        <v>58125</v>
+        <v>58127</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>136741578</v>
       </c>
       <c r="B20" t="n">
-        <v>98261</v>
+        <v>98263</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>136741588</v>
       </c>
       <c r="B21" t="n">
-        <v>98261</v>
+        <v>98263</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>136741589</v>
       </c>
       <c r="B22" t="n">
-        <v>98261</v>
+        <v>98263</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>136741590</v>
       </c>
       <c r="B23" t="n">
-        <v>98261</v>
+        <v>98263</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>136741569</v>
       </c>
       <c r="B24" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 35667-2026 artfynd.xlsx
+++ b/artfynd/A 35667-2026 artfynd.xlsx
@@ -2521,11 +2521,7 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Nattavaara, Lu lm</t>
@@ -2647,11 +2643,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Nattavaara, Lu lm</t>

--- a/artfynd/A 35667-2026 artfynd.xlsx
+++ b/artfynd/A 35667-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136741579</v>
       </c>
       <c r="B2" t="n">
-        <v>92338</v>
+        <v>92341</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>136741574</v>
       </c>
       <c r="B3" t="n">
-        <v>91149</v>
+        <v>91152</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136741584</v>
       </c>
       <c r="B4" t="n">
-        <v>91149</v>
+        <v>91152</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136741571</v>
       </c>
       <c r="B5" t="n">
-        <v>92198</v>
+        <v>92201</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136741596</v>
       </c>
       <c r="B6" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136741597</v>
       </c>
       <c r="B7" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>136741600</v>
       </c>
       <c r="B8" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>136741585</v>
       </c>
       <c r="B9" t="n">
-        <v>90927</v>
+        <v>90930</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>136741587</v>
       </c>
       <c r="B10" t="n">
-        <v>90927</v>
+        <v>90930</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>136741578</v>
       </c>
       <c r="B20" t="n">
-        <v>98263</v>
+        <v>98266</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>136741588</v>
       </c>
       <c r="B21" t="n">
-        <v>98263</v>
+        <v>98266</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>136741589</v>
       </c>
       <c r="B22" t="n">
-        <v>98263</v>
+        <v>98266</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>136741590</v>
       </c>
       <c r="B23" t="n">
-        <v>98263</v>
+        <v>98266</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>136741569</v>
       </c>
       <c r="B24" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 35667-2026 artfynd.xlsx
+++ b/artfynd/A 35667-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136741579</v>
       </c>
       <c r="B2" t="n">
-        <v>92341</v>
+        <v>92351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>136741574</v>
       </c>
       <c r="B3" t="n">
-        <v>91152</v>
+        <v>91162</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136741584</v>
       </c>
       <c r="B4" t="n">
-        <v>91152</v>
+        <v>91162</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136741571</v>
       </c>
       <c r="B5" t="n">
-        <v>92201</v>
+        <v>92211</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136741596</v>
       </c>
       <c r="B6" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136741597</v>
       </c>
       <c r="B7" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>136741600</v>
       </c>
       <c r="B8" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>136741585</v>
       </c>
       <c r="B9" t="n">
-        <v>90930</v>
+        <v>90940</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>136741587</v>
       </c>
       <c r="B10" t="n">
-        <v>90930</v>
+        <v>90940</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>136741570</v>
       </c>
       <c r="B11" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>136741575</v>
       </c>
       <c r="B12" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136741576</v>
       </c>
       <c r="B13" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>136741582</v>
       </c>
       <c r="B14" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>136741583</v>
       </c>
       <c r="B15" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>136741595</v>
       </c>
       <c r="B16" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>136741591</v>
       </c>
       <c r="B17" t="n">
-        <v>80622</v>
+        <v>80632</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>136741592</v>
       </c>
       <c r="B18" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>136741577</v>
       </c>
       <c r="B19" t="n">
-        <v>58127</v>
+        <v>58137</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>136741578</v>
       </c>
       <c r="B20" t="n">
-        <v>98266</v>
+        <v>98276</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>136741588</v>
       </c>
       <c r="B21" t="n">
-        <v>98266</v>
+        <v>98276</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>136741589</v>
       </c>
       <c r="B22" t="n">
-        <v>98266</v>
+        <v>98276</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>136741590</v>
       </c>
       <c r="B23" t="n">
-        <v>98266</v>
+        <v>98276</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>136741569</v>
       </c>
       <c r="B24" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 35667-2026 artfynd.xlsx
+++ b/artfynd/A 35667-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136741579</v>
       </c>
       <c r="B2" t="n">
-        <v>92351</v>
+        <v>92352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>136741574</v>
       </c>
       <c r="B3" t="n">
-        <v>91162</v>
+        <v>91163</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136741584</v>
       </c>
       <c r="B4" t="n">
-        <v>91162</v>
+        <v>91163</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136741571</v>
       </c>
       <c r="B5" t="n">
-        <v>92211</v>
+        <v>92212</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136741596</v>
       </c>
       <c r="B6" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136741597</v>
       </c>
       <c r="B7" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>136741600</v>
       </c>
       <c r="B8" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>136741585</v>
       </c>
       <c r="B9" t="n">
-        <v>90940</v>
+        <v>90941</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>136741587</v>
       </c>
       <c r="B10" t="n">
-        <v>90940</v>
+        <v>90941</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>136741578</v>
       </c>
       <c r="B20" t="n">
-        <v>98276</v>
+        <v>98277</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>136741588</v>
       </c>
       <c r="B21" t="n">
-        <v>98276</v>
+        <v>98277</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>136741589</v>
       </c>
       <c r="B22" t="n">
-        <v>98276</v>
+        <v>98277</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>136741590</v>
       </c>
       <c r="B23" t="n">
-        <v>98276</v>
+        <v>98277</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>136741569</v>
       </c>
       <c r="B24" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
